--- a/out/CLB4_BFR_full.xlsx
+++ b/out/CLB4_BFR_full.xlsx
@@ -108,7 +108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -135,11 +135,55 @@
         <color rgb="00000000"/>
       </top>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,6 +235,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -940,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -1073,7 +1123,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Personnel Category</t>
         </is>
@@ -1148,7 +1198,7 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Vehicle Category</t>
         </is>
@@ -1175,29 +1225,29 @@
           <t>Comm vehicles (radio shelters)</t>
         </is>
       </c>
-      <c r="V15" s="21" t="n">
+      <c r="V15" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y15" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="AB15" s="21" t="inlineStr"/>
+      <c r="AB15" s="25" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="12" t="inlineStr"/>
-      <c r="V16" s="21" t="inlineStr"/>
+      <c r="V16" s="25" t="inlineStr"/>
       <c r="Y16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" s="21" t="inlineStr"/>
+      <c r="AB16" s="25" t="inlineStr"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="12" t="inlineStr"/>
-      <c r="V17" s="21" t="inlineStr"/>
+      <c r="V17" s="25" t="inlineStr"/>
       <c r="Y17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="21" t="inlineStr"/>
+      <c r="AB17" s="25" t="inlineStr"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -1205,12 +1255,12 @@
           <t>Total Self-Propelled Vehicles | CEILING(total / 15) bays</t>
         </is>
       </c>
-      <c r="V18" s="21" t="inlineStr"/>
+      <c r="V18" s="25" t="inlineStr"/>
       <c r="Y18" s="14">
         <f>SUM(Y15:Y17)</f>
         <v/>
       </c>
-      <c r="AB18" s="21" t="inlineStr"/>
+      <c r="AB18" s="25" t="inlineStr"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -1218,7 +1268,7 @@
           <t>Maintenance Bays (CEILING bays per 15 vehicles)</t>
         </is>
       </c>
-      <c r="V19" s="21" t="n">
+      <c r="V19" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y19" s="14">
@@ -1269,7 +1319,7 @@
       <c r="V24" s="13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y24" s="21" t="inlineStr"/>
+      <c r="Y24" s="25" t="inlineStr"/>
       <c r="AB24" s="14">
         <f>ROUNDUP(AB23*V24,0)</f>
         <v/>
@@ -1304,8 +1354,86 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 200 Series; version date 2025-05-16</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_200series_05_16_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [195]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 21710-1: Electronics maintenance shops at Naval and Marine Corps activities</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="75">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y4:AF4"/>
     <mergeCell ref="A13:AF13"/>
@@ -1320,13 +1448,16 @@
     <mergeCell ref="AB24:AF24"/>
     <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="Y17:AA17"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="V15:X15"/>
     <mergeCell ref="A18:U18"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="A6:AF6"/>
@@ -1354,6 +1485,8 @@
     <mergeCell ref="V18:X18"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
@@ -1368,6 +1501,7 @@
     <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AB19:AF19"/>
@@ -1396,7 +1530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -1529,7 +1663,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Personnel Category</t>
         </is>
@@ -1604,7 +1738,7 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Vehicle Category</t>
         </is>
@@ -1631,29 +1765,29 @@
           <t>Field maintenance vehicles</t>
         </is>
       </c>
-      <c r="V15" s="21" t="n">
+      <c r="V15" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y15" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="AB15" s="21" t="inlineStr"/>
+      <c r="AB15" s="25" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="12" t="inlineStr"/>
-      <c r="V16" s="21" t="inlineStr"/>
+      <c r="V16" s="25" t="inlineStr"/>
       <c r="Y16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" s="21" t="inlineStr"/>
+      <c r="AB16" s="25" t="inlineStr"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="12" t="inlineStr"/>
-      <c r="V17" s="21" t="inlineStr"/>
+      <c r="V17" s="25" t="inlineStr"/>
       <c r="Y17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="21" t="inlineStr"/>
+      <c r="AB17" s="25" t="inlineStr"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -1661,12 +1795,12 @@
           <t>Total Self-Propelled Vehicles | CEILING(total / 15) bays</t>
         </is>
       </c>
-      <c r="V18" s="21" t="inlineStr"/>
+      <c r="V18" s="25" t="inlineStr"/>
       <c r="Y18" s="14">
         <f>SUM(Y15:Y17)</f>
         <v/>
       </c>
-      <c r="AB18" s="21" t="inlineStr"/>
+      <c r="AB18" s="25" t="inlineStr"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -1674,7 +1808,7 @@
           <t>Maintenance Bays (CEILING bays per 15 vehicles)</t>
         </is>
       </c>
-      <c r="V19" s="21" t="n">
+      <c r="V19" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y19" s="14">
@@ -1725,7 +1859,7 @@
       <c r="V24" s="13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y24" s="21" t="inlineStr"/>
+      <c r="Y24" s="25" t="inlineStr"/>
       <c r="AB24" s="14">
         <f>ROUNDUP(AB23*V24,0)</f>
         <v/>
@@ -1760,8 +1894,99 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 200 Series; version date 2025-05-16</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_200series_05_16_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [196]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 21730-1: This field maintenance shop provides specialized work areas for</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>UoM source: CCN_VOCABULARY.json (Appendix A 2019-06-27); Series PDF heading omitted UoM, ratifier should verify against current Series text</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="76">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y4:AF4"/>
     <mergeCell ref="A13:AF13"/>
@@ -1776,13 +2001,16 @@
     <mergeCell ref="AB24:AF24"/>
     <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="Y17:AA17"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="V15:X15"/>
     <mergeCell ref="A18:U18"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="A6:AF6"/>
@@ -1798,6 +2026,7 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="V16:X16"/>
     <mergeCell ref="C5:L5"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="V19:X19"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
@@ -1810,6 +2039,8 @@
     <mergeCell ref="V18:X18"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
@@ -1824,6 +2055,7 @@
     <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AB19:AF19"/>
@@ -1852,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -2121,11 +2353,64 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 400 (Maintenance &amp; Production; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 441 12 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="56">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
@@ -2137,6 +2422,7 @@
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
@@ -2151,6 +2437,7 @@
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
@@ -2159,6 +2446,7 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -2196,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -2454,7 +2742,7 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="22">
+      <c r="H37" s="26">
         <f>AB16</f>
         <v/>
       </c>
@@ -2465,11 +2753,64 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 400 (Maintenance &amp; Production; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 451 10 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="56">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
@@ -2481,6 +2822,7 @@
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
@@ -2495,6 +2837,7 @@
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
@@ -2503,6 +2846,7 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -65726,7 +66070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -66035,11 +66379,77 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 100 Series; version date 2026-02-11</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_100series_02_11_2026.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [205]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Table 14345-1 (Armory); loading driver: Installation Military Strength</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="57">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
@@ -66051,6 +66461,7 @@
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
@@ -66065,6 +66476,7 @@
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
@@ -66073,6 +66485,7 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -66082,6 +66495,7 @@
     <mergeCell ref="AB7:AF7"/>
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>
@@ -66110,7 +66524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -66243,7 +66657,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Personnel Category</t>
         </is>
@@ -66318,7 +66732,7 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Vehicle Category</t>
         </is>
@@ -66345,13 +66759,13 @@
           <t>Light Utility Vehicles (JLTV-class M1280, M1279)</t>
         </is>
       </c>
-      <c r="V15" s="21" t="n">
+      <c r="V15" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y15" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="AB15" s="21" t="inlineStr"/>
+      <c r="AB15" s="25" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -66359,13 +66773,13 @@
           <t>Medium / Heavy Cargo (AMK23A1, AMK27A1)</t>
         </is>
       </c>
-      <c r="V16" s="21" t="n">
+      <c r="V16" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y16" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="AB16" s="21" t="inlineStr"/>
+      <c r="AB16" s="25" t="inlineStr"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -66373,13 +66787,13 @@
           <t>Wrecker / Recovery (AMK36)</t>
         </is>
       </c>
-      <c r="V17" s="21" t="n">
+      <c r="V17" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y17" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AB17" s="21" t="inlineStr"/>
+      <c r="AB17" s="25" t="inlineStr"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -66387,12 +66801,12 @@
           <t>Total Self-Propelled Vehicles | CEILING(total / 30) bays</t>
         </is>
       </c>
-      <c r="V18" s="21" t="inlineStr"/>
+      <c r="V18" s="25" t="inlineStr"/>
       <c r="Y18" s="14">
         <f>SUM(Y15:Y17)</f>
         <v/>
       </c>
-      <c r="AB18" s="21" t="inlineStr"/>
+      <c r="AB18" s="25" t="inlineStr"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -66400,7 +66814,7 @@
           <t>Maintenance Bays (CEILING bays per 30 vehicles)</t>
         </is>
       </c>
-      <c r="V19" s="21" t="n">
+      <c r="V19" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y19" s="14">
@@ -66451,7 +66865,7 @@
       <c r="V24" s="13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y24" s="21" t="inlineStr"/>
+      <c r="Y24" s="25" t="inlineStr"/>
       <c r="AB24" s="14">
         <f>ROUNDUP(AB23*V24,0)</f>
         <v/>
@@ -66486,8 +66900,86 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 200 Series; version date 2025-05-16</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_200series_05_16_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [188]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 3 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 21451-1: This facility provides work areas for Fleet Marine Force (FMF) units to</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="75">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y4:AF4"/>
     <mergeCell ref="A13:AF13"/>
@@ -66502,13 +66994,16 @@
     <mergeCell ref="AB24:AF24"/>
     <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="Y17:AA17"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="V15:X15"/>
     <mergeCell ref="A18:U18"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="A6:AF6"/>
@@ -66536,6 +67031,8 @@
     <mergeCell ref="V18:X18"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
@@ -66550,6 +67047,7 @@
     <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AB19:AF19"/>
@@ -66578,7 +67076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -66847,11 +67345,90 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 200 Series; version date 2025-05-16</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_200series_05_16_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [188]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 21455-1: REQUIREMENTS. Vehicle wash platforms equipped with hose</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="58">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
@@ -66860,9 +67437,11 @@
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
@@ -66877,6 +67456,7 @@
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
@@ -66885,6 +67465,7 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -66894,6 +67475,7 @@
     <mergeCell ref="AB7:AF7"/>
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>
@@ -66922,7 +67504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -67174,7 +67756,7 @@
       <c r="V20" s="13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y20" s="21" t="inlineStr"/>
+      <c r="Y20" s="25" t="inlineStr"/>
       <c r="AB20" s="14">
         <f>ROUNDUP(AB17*V20,0)</f>
         <v/>
@@ -67213,8 +67795,60 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 600 (Administrative; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 610 72 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="49">
     <mergeCell ref="A10:AF10"/>
     <mergeCell ref="Y20:AA20"/>
     <mergeCell ref="Y4:AF4"/>
@@ -67223,6 +67857,7 @@
     <mergeCell ref="A16:U16"/>
     <mergeCell ref="A19:AF19"/>
     <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="A9:AF9"/>
@@ -67232,6 +67867,7 @@
     <mergeCell ref="A11:AF11"/>
     <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
@@ -67244,10 +67880,12 @@
     <mergeCell ref="A17:AA17"/>
     <mergeCell ref="A20:U20"/>
     <mergeCell ref="R4:X4"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="AB17:AF17"/>
@@ -67281,7 +67919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -67539,7 +68177,7 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="22">
+      <c r="H37" s="26">
         <f>AB16</f>
         <v/>
       </c>
@@ -67550,11 +68188,103 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 100 Series; version date 2026-02-11</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_100series_02_11_2026.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [189, 190]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_190_table_1 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_190_table_2 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_190_table_3 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="59">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
@@ -67563,9 +68293,11 @@
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
@@ -67576,10 +68308,12 @@
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
@@ -67588,6 +68322,7 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -67597,6 +68332,7 @@
     <mergeCell ref="AB7:AF7"/>
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>
@@ -67625,7 +68361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -67841,7 +68577,7 @@
       <c r="V14" s="13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y14" s="21" t="inlineStr"/>
+      <c r="Y14" s="25" t="inlineStr"/>
       <c r="AB14" s="14">
         <f>ROUNDUP(AB11*V14,0)</f>
         <v/>
@@ -67886,18 +68622,112 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 100 Series; version date 2026-02-11</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_100series_02_11_2026.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [200, 201, 202, 203]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 24 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 14326-1: This facility is necessary for manning, equipping, and training for EOD</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>UoM source: CCN_VOCABULARY.json (Appendix A 2019-06-27); Series PDF heading omitted UoM, ratifier should verify against current Series text</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="47">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y4:AF4"/>
     <mergeCell ref="A13:AF13"/>
     <mergeCell ref="Y14:AA14"/>
     <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="V9:X9"/>
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="A6:AF6"/>
@@ -67907,15 +68737,18 @@
     <mergeCell ref="A7:AF7"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="A10:U10"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -67923,6 +68756,7 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="V14:X14"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AB10:AF10"/>

--- a/out/CLB4_BFR_full.xlsx
+++ b/out/CLB4_BFR_full.xlsx
@@ -20,6 +20,7 @@
     <sheet name="21730" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="44112" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="45110" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="53010" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'14345'!$A$1:$AF$37</definedName>
@@ -32,6 +33,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'21730'!$A$1:$AF$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'44112'!$A$1:$AF$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'45110'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'53010'!$A$1:$AF$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -616,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF20"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -944,16 +946,37 @@
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>530 10</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>DISP &amp; OUT PATIENT CLINIC</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="E19" s="6">
+        <f>'53010'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="9">
-        <f>SUM(E9:E18)</f>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="9">
+        <f>SUM(E9:E19)</f>
         <v/>
       </c>
     </row>
@@ -2084,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF43"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -2369,7 +2392,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>FC 2-000-05N citation: TBD pending Series 400 (Maintenance &amp; Production; not yet supplied)</t>
+          <t>FC 2-000-05N 400 Series; version date 2025-11-19</t>
         </is>
       </c>
       <c r="C41" s="21" t="n"/>
@@ -2382,7 +2405,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>CCN 441 12 not in supplied Series 100/200 PDFs</t>
+          <t>Source PDF: fc_2_000_05n_400series_11_19_2025.pdf</t>
         </is>
       </c>
       <c r="C42" s="21" t="n"/>
@@ -2395,7 +2418,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+          <t>Pages: [46]</t>
         </is>
       </c>
       <c r="C43" s="21" t="n"/>
@@ -2405,8 +2428,34 @@
       <c r="G43" s="21" t="n"/>
       <c r="H43" s="22" t="n"/>
     </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 44112-1: DESCRIPTION. This category code includes general purpose storage</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="58">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
@@ -2419,6 +2468,7 @@
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
@@ -2456,6 +2506,7 @@
     <mergeCell ref="AB7:AF7"/>
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>
@@ -2484,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF43"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -2769,7 +2820,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>FC 2-000-05N citation: TBD pending Series 400 (Maintenance &amp; Production; not yet supplied)</t>
+          <t>FC 2-000-05N 400 Series; version date 2025-11-19</t>
         </is>
       </c>
       <c r="C41" s="21" t="n"/>
@@ -2782,7 +2833,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>CCN 451 10 not in supplied Series 100/200 PDFs</t>
+          <t>Source PDF: fc_2_000_05n_400series_11_19_2025.pdf</t>
         </is>
       </c>
       <c r="C42" s="21" t="n"/>
@@ -2795,7 +2846,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+          <t>Pages: [50, 51]</t>
         </is>
       </c>
       <c r="C43" s="21" t="n"/>
@@ -2805,8 +2856,34 @@
       <c r="G43" s="21" t="n"/>
       <c r="H43" s="22" t="n"/>
     </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 2 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 45110-1: DESCRIPTION. This category group consists of non-covered storage</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="58">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
@@ -2819,6 +2896,7 @@
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
@@ -2856,12 +2934,421 @@
     <mergeCell ref="AB7:AF7"/>
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>
     <mergeCell ref="AB10:AF10"/>
     <mergeCell ref="V13:X13"/>
     <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>530 10</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>DISP &amp; OUT PATIENT CLINIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 530 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE SPACE CALCULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>BAS Personnel Space</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>SF / Person</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>BAS Medical Officers / IDC</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="14">
+        <f>V9*Y9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Hospital Corpsmen / Field Med Tech / Dental Asst</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB10" s="14">
+        <f>V10*Y10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Total NSF</t>
+        </is>
+      </c>
+      <c r="AB11" s="14">
+        <f>SUM(AB9:AB10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1"/>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SPACE REQUIREMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>NTG Factor = 1.33, Required GSF = ROUNDUP(NSF * NTG, 0)</t>
+        </is>
+      </c>
+      <c r="V14" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y14" s="25" t="inlineStr"/>
+      <c r="AB14" s="14">
+        <f>ROUNDUP(AB11*V14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB14</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 500 Series; version date 2023-03-17</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_500series_03_17_2023.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [8]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 53010-1: GENERAL. Free Standing Clinic, outpatient clinic, which occupies a</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="46">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="Y14:AA14"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="AB14:AF14"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="A14:U14"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="A7:AF7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="A11:AA11"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0"/>
@@ -17588,8 +18075,16 @@
       <c r="B20" t="n">
         <v>16</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -24502,8 +24997,16 @@
       <c r="B138" t="n">
         <v>134</v>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>14326</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>14326</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -24785,8 +25288,16 @@
       <c r="B143" t="n">
         <v>139</v>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>21710</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>21710</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -27494,8 +28005,16 @@
       <c r="B190" t="n">
         <v>186</v>
       </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -27541,8 +28060,16 @@
       <c r="B191" t="n">
         <v>187</v>
       </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -27863,8 +28390,16 @@
       <c r="B197" t="n">
         <v>193</v>
       </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>21451</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>21451</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -30382,8 +30917,16 @@
       <c r="B242" t="n">
         <v>238</v>
       </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G242" t="inlineStr">
         <is>
           <t>M29112</t>
@@ -30433,8 +30976,16 @@
       <c r="B243" t="n">
         <v>239</v>
       </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G243" t="inlineStr">
         <is>
           <t>M29112</t>
@@ -39109,8 +39660,16 @@
       <c r="B391" t="n">
         <v>387</v>
       </c>
-      <c r="C391" t="inlineStr"/>
-      <c r="D391" t="inlineStr"/>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G391" t="inlineStr">
         <is>
           <t>M29112</t>
@@ -39156,8 +39715,16 @@
       <c r="B392" t="n">
         <v>388</v>
       </c>
-      <c r="C392" t="inlineStr"/>
-      <c r="D392" t="inlineStr"/>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G392" t="inlineStr">
         <is>
           <t>M29112</t>
@@ -39203,8 +39770,16 @@
       <c r="B393" t="n">
         <v>389</v>
       </c>
-      <c r="C393" t="inlineStr"/>
-      <c r="D393" t="inlineStr"/>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G393" t="inlineStr">
         <is>
           <t>M29112</t>
@@ -39250,8 +39825,16 @@
       <c r="B394" t="n">
         <v>390</v>
       </c>
-      <c r="C394" t="inlineStr"/>
-      <c r="D394" t="inlineStr"/>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>21730</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>21730</t>
+        </is>
+      </c>
       <c r="G394" t="inlineStr">
         <is>
           <t>M29112</t>
@@ -41553,8 +42136,16 @@
       <c r="B435" t="n">
         <v>431</v>
       </c>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G435" t="inlineStr">
         <is>
           <t>M29113</t>
@@ -41604,8 +42195,16 @@
       <c r="B436" t="n">
         <v>432</v>
       </c>
-      <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G436" t="inlineStr">
         <is>
           <t>M29113</t>
@@ -50280,8 +50879,16 @@
       <c r="B584" t="n">
         <v>580</v>
       </c>
-      <c r="C584" t="inlineStr"/>
-      <c r="D584" t="inlineStr"/>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G584" t="inlineStr">
         <is>
           <t>M29113</t>
@@ -50327,8 +50934,16 @@
       <c r="B585" t="n">
         <v>581</v>
       </c>
-      <c r="C585" t="inlineStr"/>
-      <c r="D585" t="inlineStr"/>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G585" t="inlineStr">
         <is>
           <t>M29113</t>
@@ -50374,8 +50989,16 @@
       <c r="B586" t="n">
         <v>582</v>
       </c>
-      <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr"/>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G586" t="inlineStr">
         <is>
           <t>M29113</t>
@@ -50421,8 +51044,16 @@
       <c r="B587" t="n">
         <v>583</v>
       </c>
-      <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>21730</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>21730</t>
+        </is>
+      </c>
       <c r="G587" t="inlineStr">
         <is>
           <t>M29113</t>
@@ -53428,8 +54059,16 @@
       <c r="B640" t="n">
         <v>636</v>
       </c>
-      <c r="C640" t="inlineStr"/>
-      <c r="D640" t="inlineStr"/>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>21710</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>21710</t>
+        </is>
+      </c>
       <c r="G640" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -53656,8 +54295,16 @@
       <c r="B644" t="n">
         <v>640</v>
       </c>
-      <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr"/>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G644" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -53707,8 +54354,16 @@
       <c r="B645" t="n">
         <v>641</v>
       </c>
-      <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr"/>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>61072</t>
+        </is>
+      </c>
       <c r="G645" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -60743,8 +61398,16 @@
       <c r="B765" t="n">
         <v>761</v>
       </c>
-      <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr"/>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="G765" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -60790,8 +61453,16 @@
       <c r="B766" t="n">
         <v>762</v>
       </c>
-      <c r="C766" t="inlineStr"/>
-      <c r="D766" t="inlineStr"/>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="G766" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -60837,8 +61508,16 @@
       <c r="B767" t="n">
         <v>763</v>
       </c>
-      <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr"/>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="G767" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -60884,8 +61563,16 @@
       <c r="B768" t="n">
         <v>764</v>
       </c>
-      <c r="C768" t="inlineStr"/>
-      <c r="D768" t="inlineStr"/>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="G768" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -60931,8 +61618,16 @@
       <c r="B769" t="n">
         <v>765</v>
       </c>
-      <c r="C769" t="inlineStr"/>
-      <c r="D769" t="inlineStr"/>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="G769" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -60978,8 +61673,16 @@
       <c r="B770" t="n">
         <v>766</v>
       </c>
-      <c r="C770" t="inlineStr"/>
-      <c r="D770" t="inlineStr"/>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="G770" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -66070,7 +66773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF44"/>
+  <dimension ref="A1:AF49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -66444,8 +67147,73 @@
       <c r="G44" s="21" t="n"/>
       <c r="H44" s="22" t="n"/>
     </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    up to 2,000 | 576</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2,001 - 4,000 | 880</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    4,001 - 7,500 | 1,200</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    7,501 - 10,000 | 1,508</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Over 10,000 | Add 0.1 sq ft per person</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="62">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
@@ -66454,10 +67222,12 @@
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
     <mergeCell ref="V9:X9"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="A16:AA16"/>
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
@@ -66467,11 +67237,13 @@
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="B47:H47"/>
     <mergeCell ref="Y12:AA12"/>
     <mergeCell ref="AB9:AF9"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
@@ -66486,6 +67258,7 @@
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
     <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B48:H48"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -67504,7 +68277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF43"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -67811,7 +68584,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>FC 2-000-05N citation: TBD pending Series 600 (Administrative; not yet supplied)</t>
+          <t>FC 2-000-05N 600 Series; version date 2023-03-02</t>
         </is>
       </c>
       <c r="C41" s="21" t="n"/>
@@ -67824,7 +68597,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>CCN 610 72 not in supplied Series 100/200 PDFs</t>
+          <t>Source PDF: fc_2_000_05n_600series_03_02_2023.pdf</t>
         </is>
       </c>
       <c r="C42" s="21" t="n"/>
@@ -67837,7 +68610,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+          <t>Pages: [39]</t>
         </is>
       </c>
       <c r="C43" s="21" t="n"/>
@@ -67847,8 +68620,34 @@
       <c r="G43" s="21" t="n"/>
       <c r="H43" s="22" t="n"/>
     </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 61072-1: This category code is for a Fleet Marine Force (FMF) facility and provides</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="51">
     <mergeCell ref="A10:AF10"/>
     <mergeCell ref="Y20:AA20"/>
     <mergeCell ref="Y4:AF4"/>
@@ -67864,6 +68663,7 @@
     <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="V15:X15"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="A11:AF11"/>
     <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
@@ -67895,6 +68695,7 @@
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="Y15:AA15"/>
     <mergeCell ref="A8:AF8"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V20:X20"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="M4:Q4"/>
@@ -67919,7 +68720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF46"/>
+  <dimension ref="A1:AF61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -68256,7 +69057,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  page_190_table_2 (); loading driver: TBD</t>
+          <t xml:space="preserve">    Non-mechanized CESE and SABAR (ex: Small (&lt;10FT) Fuel Water SIXCON, Motors, Pumps, A 19 168 1.50 Generators, TRICONS)</t>
         </is>
       </c>
       <c r="C45" s="21" t="n"/>
@@ -68269,7 +69070,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  page_190_table_3 (); loading driver: TBD</t>
+          <t xml:space="preserve">    Vehicles and non-mechanized CESE and Medium (10FT- SABAR (ex: Passenger Vehicles, B 32 288 1.75 20FT) HMMWV, Light Plant, Fork Lifts, Small Zodiac Boats)</t>
         </is>
       </c>
       <c r="C46" s="21" t="n"/>
@@ -68279,8 +69080,203 @@
       <c r="G46" s="21" t="n"/>
       <c r="H46" s="22" t="n"/>
     </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Large CESE and SABAR (ex: MTVR, Fuel Large (20FT-30FT) C 46 408 1.75 Trucks, Boats &lt; 30FT)</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Extra Large CESE and SABAR (ex: Boats Extra Large (30FT- &gt; 30FT, Scrapers, Water Well, Semi D 59 528 2.00 40FT) Trailers)</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Extra Large CESE and SABAR (ex: Boats Extra Large (40FT- &gt; 40FT, Scrapers, Water Well, Semi E 72 648 2.00 50FT) Trailers)</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Extra Large (50FT- Extra Large CESE and SABAR (ex: Boats F 86 768 2.25 60FT) &gt; 50 FT, Semi Trailers, lowboy 55T)</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="22" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Extra Large CESE and SABAR (ex: 11M Extra Large (60FT- Rib with Prime Mover; 40PB with Prime G 99 888 2.25 70FT) Mover)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="22" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_190_table_2 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="22" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_190_table_3 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="22" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1A | 5</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="22" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    A | 10</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="21" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="22" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1B | 15</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="22" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    B | 20</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="21" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="22" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    C | 30</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="21" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="22" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    D | 40</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="21" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="22" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    E | 50</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="22" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    F | 60</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="21" t="n"/>
+      <c r="E61" s="21" t="n"/>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="21" t="n"/>
+      <c r="H61" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="74">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
@@ -68289,28 +69285,38 @@
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
     <mergeCell ref="V9:X9"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="A16:AA16"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B51:H51"/>
     <mergeCell ref="Y7:AA7"/>
     <mergeCell ref="B45:H45"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B50:H50"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B54:H54"/>
     <mergeCell ref="Y12:AA12"/>
     <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="B59:H59"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B52:H52"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
     <mergeCell ref="B43:H43"/>
@@ -68323,16 +69329,21 @@
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
     <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B48:H48"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
+    <mergeCell ref="B60:H60"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B61:H61"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="AB13:AF13"/>
     <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="B57:H57"/>
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>

--- a/out/CLB4_BFR_full.xlsx
+++ b/out/CLB4_BFR_full.xlsx
@@ -21,6 +21,18 @@
     <sheet name="44112" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="45110" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="53010" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="85210" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="85122" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="85121" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="87210" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="87250" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="87230" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="83143" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="83141" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="81160" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="88010" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="85235" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="85240" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'14345'!$A$1:$AF$37</definedName>
@@ -34,6 +46,18 @@
     <definedName name="_xlnm.Print_Area" localSheetId="11">'44112'!$A$1:$AF$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'45110'!$A$1:$AF$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'53010'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'85210'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'85122'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'85121'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'87210'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'87250'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'87230'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'83143'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'83141'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'81160'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'88010'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="24">'85235'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="25">'85240'!$A$1:$AF$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,9 +65,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0\ &quot;GSF&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0\ &quot;GSY&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0\ &quot;LF&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0\ &quot;EA&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0\ &quot;KW&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0\ &quot;MI&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -185,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -251,6 +279,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -618,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF21"/>
+  <dimension ref="A1:AF33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -967,16 +1007,268 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>852 10</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>PARKING AREA</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="E20" s="6">
+        <f>'85210'!H37</f>
+        <v/>
+      </c>
+    </row>
     <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>851 22</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>VEHICLE STAGING AREA</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="E21" s="6">
+        <f>'85122'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>851 21</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>VEH. PARK, UNSURFACED</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="E22" s="6">
+        <f>'85121'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>872 10</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>SECURTY/PERIMTR FENCE/WALL</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="E23" s="6">
+        <f>'87210'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>872 50</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY GATE</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="E24" s="6">
+        <f>'87250'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>872 30</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>MECH SEC BARRICADE</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E25" s="6">
+        <f>'87230'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>831 43</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>HAZ WASTE BLDG</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="E26" s="6">
+        <f>'83143'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>831 41</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>HAZARD WSTE STOR &amp; TRANSFR</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="E27" s="6">
+        <f>'83141'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>811 60</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>STANDBY GENERATOR PLANT</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="E28" s="6">
+        <f>'81160'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>880 10</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>FIRE ALARM COMM LINES</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="E29" s="6">
+        <f>'88010'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>852 35</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>OTHER PAVED AREA</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="E30" s="6">
+        <f>'85235'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>852 40</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>MISC OPEN STRG/LAYDOWN</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="E31" s="6">
+        <f>'85240'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="9">
-        <f>SUM(E9:E19)</f>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="9">
+        <f>SUM(E9:E31)</f>
         <v/>
       </c>
     </row>
@@ -3365,6 +3657,2650 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>852 10</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>PARKING AREA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 852 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>PARKING AREA (Loading driver: Organizational Vehicle Parking (count of CLB-4 motor pool vehicles); FAC 8521; cited factor 75 SY/vehicle for FMF Ground Units (50 SY/vehicle if &gt;50% are &lt;=18ft x 6.5ft); UoM=SY; user-supplied spec 2026-04-30 pending FC 2-000-05N Series 800 cross-check)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="26">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [60, 61, 62, 63]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Table 85210-1 (); loading driver: Personnel</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Bank and Credit Union, when not included in a Community Shopping | 2% of customers served</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Cafeteria, Civilian, when not included in a Community Shopping Center | 15% of seating capacity</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Central Food Preparation Facilities | 38% of employees</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Chapels | 30% of seating capacity</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Child Development Centers (Patron Parking) | 10% of children served</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Child Development Centers (Staff Parking) | 80% of staff</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="22" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Commissary Stores, Food Sales, when not included in a Community Shopping Center | Contact DeCA for parking requirements.</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="22" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Community Shopping Center, including such elements as Main Exchange, Miscellaneous Shops, Restaurant, Commissary Stores, Food Sales, Bank, Theater, Post Office | 4% of customers served</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="22" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ... and 3 more rows; see audit/PLANNING_FACTORS.yaml CCN 85210</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="22" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_62_table_2 (); loading driver: Personnel</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="22" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Family Housing | 2.5 spaces per living unit</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="21" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="22" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Field House, combined with Football and Baseball Facilities | 1% of military strength</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="22" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Fire Stations | 100% of largest shift</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="21" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="22" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Guard Houses, Brigs, Military Police Stations | 30% of guard and staff strength</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="21" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="22" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Fitness Center | 1 percent of military strength served</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="21" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="22" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Laundries and Dry Cleaning Plants | 38% of employees</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="22" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Libraries (Central) | 1 space for each 46 m2 (500 ft2) of gross floor area</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="21" t="n"/>
+      <c r="E61" s="21" t="n"/>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="21" t="n"/>
+      <c r="H61" s="22" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Libraries (Branch) | 8 spaces</t>
+        </is>
+      </c>
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="21" t="n"/>
+      <c r="E62" s="21" t="n"/>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="21" t="n"/>
+      <c r="H62" s="22" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ... and 10 more rows; see audit/PLANNING_FACTORS.yaml CCN 85210</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="21" t="n"/>
+      <c r="E63" s="21" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="22" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="B64" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_63_table_3 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="21" t="n"/>
+      <c r="E64" s="21" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="n"/>
+      <c r="H64" s="22" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Security Offices: Population served 10,001 and over | To be based on a special study.</t>
+        </is>
+      </c>
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="21" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="22" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="B66" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Service Clubs (Open Mess and Club Facility) | 2% of military strength served</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="21" t="n"/>
+      <c r="E66" s="21" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="22" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Swimming Pools | 20 percent of the pool capacity</t>
+        </is>
+      </c>
+      <c r="C67" s="21" t="n"/>
+      <c r="D67" s="21" t="n"/>
+      <c r="E67" s="21" t="n"/>
+      <c r="F67" s="21" t="n"/>
+      <c r="G67" s="21" t="n"/>
+      <c r="H67" s="22" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="B68" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Temporary Lodging Facilities | 90% of bedrooms</t>
+        </is>
+      </c>
+      <c r="C68" s="21" t="n"/>
+      <c r="D68" s="21" t="n"/>
+      <c r="E68" s="21" t="n"/>
+      <c r="F68" s="21" t="n"/>
+      <c r="G68" s="21" t="n"/>
+      <c r="H68" s="22" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Theaters, when not included in a Community Shopping Center | 25% of seating capacity</t>
+        </is>
+      </c>
+      <c r="C69" s="21" t="n"/>
+      <c r="D69" s="21" t="n"/>
+      <c r="E69" s="21" t="n"/>
+      <c r="F69" s="21" t="n"/>
+      <c r="G69" s="21" t="n"/>
+      <c r="H69" s="22" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="B70" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Training Buildings (Staff Parking) | 70% of staff</t>
+        </is>
+      </c>
+      <c r="C70" s="21" t="n"/>
+      <c r="D70" s="21" t="n"/>
+      <c r="E70" s="21" t="n"/>
+      <c r="F70" s="21" t="n"/>
+      <c r="G70" s="21" t="n"/>
+      <c r="H70" s="22" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="B71" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Training Buildings (Student Parking) | 60% of students</t>
+        </is>
+      </c>
+      <c r="C71" s="21" t="n"/>
+      <c r="D71" s="21" t="n"/>
+      <c r="E71" s="21" t="n"/>
+      <c r="F71" s="21" t="n"/>
+      <c r="G71" s="21" t="n"/>
+      <c r="H71" s="22" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="B72" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Warehouses | 40% of employees</t>
+        </is>
+      </c>
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="21" t="n"/>
+      <c r="E72" s="21" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="85">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B71:H71"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="M4:Q4"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="B69:H69"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>851 22</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>VEHICLE STAGING AREA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 851 22  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>VEHICLE STAGING AREA (Loading driver: Vehicle Staging Area for mount-out operations (SY); FAC 8523; sized by mission scale not by parked-vehicle count; CLB-4 placeholder 5000 SY pending unit doctrine input)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="26">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [59]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 85122-1: DEFINITION. This category code represents surfaced areas for the</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>851 21</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>VEH. PARK, UNSURFACED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 851 21  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>VEH. PARK, UNSURFACED (Loading driver: Vehicular Parking Unsurfaced (SY); FAC 8522; calculated using 85210 criteria when used; CLB-4 sets to 0 because primary parking is paved per 85210)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="26">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [59]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 85121-1: DEFINITION. An unpaved surface for parking and/or staging private</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>872 10</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>SECURTY/PERIMTR FENCE/WALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>SECURTY/PERIMTR FENCE/WALL (Loading driver: Station Security and Perimeter Fencing (LF); FAC 8721; standard 7-ft chain link with 1.5-ft outriggers and 3 strands BB; min 50-150 ft from buildings/critical supplies; SRC I/II ammo fence per DoDM 5100.76 + UFC 4-022-03; CLB-4 placeholder 2000 LF pending compound perimeter survey)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="27">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [70, 71, 72]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Table 87210-1 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Magazines storing SRC I &amp; II A&amp;E | Restricted Areas — as defined in DoDM 5100.76 | Fence fabric shall be chain link, i.e., galvanized, aluminized, or plastic- coated woven steel, 2-inch square mesh made from 9- gauge diameter wire, excluding coating that meets Federal Specification RR-F-191K. | Refer to DoDM 5100.76</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Non-metallic Security Fence Requirement | Where restrictions of visibility into activity is desired. | Wooden Security fence | Refer to OPNAVINST 5530.14E</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    At radio direction-finder structures. | Wooden Security fence</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Where chain link materials are not available. | Wooden Security fence</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Protection of sports facilities, users and spectators | Athletic courts. | Chain link. | 10-12 | --</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Swimming pools. | Chain link or decorative wood. | 6 | --</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="22" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Playgrounds. | Chain link or decorative wood. | 5 | --</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="22" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Snow fencing | Where drifting snow is a problem. | Picket interwoven with wire- studded metal posts | 4 | --</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="22" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ... and 12 more rows; see audit/PLANNING_FACTORS.yaml CCN 87210</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="22" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_72_table_2 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="67">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>872 50</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>ENTRY GATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 50  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>ENTRY GATE (Loading driver: Entry Gate (LF); FAC 8721; CCN added Jan 2024; CLB-4 default 30 LF for 1-2 main gates pending site survey)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="27">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [73]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 87250-1: ENTRY GATE. An entry gate is the frame, gate, or other apparatus that</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -17060,6 +19996,3198 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>872 30</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>MECH SEC BARRICADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 30  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>MECH SEC BARRICADE (Loading driver: Mechanical Security Barricade (EA); FAC 1458; drop arm barriers at gates; CLB-4 default 2 EA (one per gate))</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="28">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [73]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 2 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 87230-1: DEFINITION. Mechanically operated barricade consisting of pop-up</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>831 43</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>HAZ WASTE BLDG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 831 43  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>HAZ WASTE BLDG (Loading driver: Hazardous Waste Storage Building (SF); FAC 4423; 150-meter buffer from inhabited areas, ammo, or POL stores; short-term &lt;90 days vs long-term &gt;90 days; CLB-4 placeholder 400 SF for unit HAZMAT point)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [42]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 83143-1: DEFINITION. Use this category code for facilities that are buildings used</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>831 41</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>HAZARD WSTE STOR &amp; TRANSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 831 41  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>HAZARD WSTE STOR &amp; TRANSFR (Loading driver: Hazardous Waste Storage and Transfer Facility (EA); FAC 8926; non-building structures; same 150-meter buffer rule; CLB-4 default 1 EA)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [40]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 3 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 83141-1: DEFINITION. Use this category code for facilities that are structures (non-</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>811 60</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>STANDBY GENERATOR PLANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 811 60  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>STANDBY GENERATOR PLANT (Loading driver: Standby Generator Plant (KW); FAC 8112; mission-essential standby power; CLB-4 placeholder 150 KW pending engineering load study)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="29">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [17]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 81160-1: DEFINITION. Standby generator plants include all necessary equipment</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>UoM source: CCN_VOCABULARY.json (Appendix A 2019-06-27); Series PDF heading omitted UoM, ratifier should verify against current Series text</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="59">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>880 10</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>FIRE ALARM COMM LINES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 880 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRE ALARM COMM LINES (Loading driver: Fire Alarm System (MI); FAC 1351; linear miles of fire-alarm wiring across CLB-4 compound; placeholder 1 MI pending site survey)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="30">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [74]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 3 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 88010-1: FIRE ALARM SYSTEM. Fire alarm systems are of two general types:</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>UoM source: CCN_VOCABULARY.json (Appendix A 2019-06-27); Series PDF heading omitted UoM, ratifier should verify against current Series text</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="59">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>852 35</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>OTHER PAVED AREA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 852 35  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>OTHER PAVED AREA (Loading driver: Other Paved Areas Not in 100/400 Series (SY); FAC 8526; miscellaneous hardstand; CLB-4 placeholder 1000 SY)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="26">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [9, 64]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 85235-1: OTHER PAVED AREAS NOT CODED IN THE 100 OR 400 SERIES.</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>852 40</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>MISC OPEN STRG/LAYDOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 852 40  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>MISC OPEN STRG/LAYDOWN (Loading driver: Misc Open Storage/Laydown Area Paved (SY); FAC 8526; PW open storage allowances per Table 85240-1; CLB-4 placeholder 2000 SY pending shop-type breakdown)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="26">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [9, 10, 11, 12, 65]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_12_table_1 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    130 | Communication &amp; Navigational Aid | SF | 13, 5</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Airfield Lighting | LF | 6</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    140 | Land Operations Facilities | SF | 7.5</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    150 | Waterfront Operational Facilities | SF FB | 5 5 x 103</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    170 | Training Facilities | SF | 7.5</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    210 | Maintenance. Shops &amp; Facilities | SF | 7.5</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="22" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    220 | Production Buildings. &amp; Plants | SF | 7.5</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="22" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    310 | Research, Development &amp; Test Bldg. | SF | 7.5</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="22" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ... and 9 more rows; see audit/PLANNING_FACTORS.yaml CCN 85240</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="22" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_12_table_2 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="22" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Table 85240-1 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="21" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="22" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    E | 780</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="22" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    F | 1,180</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="21" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="70">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
   <pageSetup orientation="portrait" scale="84"/>

--- a/out/CLB4_BFR_full.xlsx
+++ b/out/CLB4_BFR_full.xlsx
@@ -21,18 +21,20 @@
     <sheet name="44112" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="45110" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="53010" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="85210" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="85122" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="85121" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="87210" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="87250" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="87230" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="83143" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="83141" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="81160" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="88010" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="85235" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="85240" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="54010" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="72210" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="85210" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="85122" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="85121" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="87210" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="87250" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="87230" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="83143" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="83141" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="81160" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="88010" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="85235" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="85240" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'14345'!$A$1:$AF$37</definedName>
@@ -46,18 +48,20 @@
     <definedName name="_xlnm.Print_Area" localSheetId="11">'44112'!$A$1:$AF$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'45110'!$A$1:$AF$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'53010'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'85210'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'85122'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'85121'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'87210'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="18">'87250'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="19">'87230'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="20">'83143'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="21">'83141'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="22">'81160'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="23">'88010'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="24">'85235'!$A$1:$AF$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="25">'85240'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'54010'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'72210'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'85210'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'85122'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'85121'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'87210'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'87250'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'87230'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'83143'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'83141'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="24">'81160'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="25">'88010'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="26">'85235'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="27">'85240'!$A$1:$AF$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -658,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF33"/>
+  <dimension ref="A1:AF35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -1010,265 +1014,307 @@
     <row r="20">
       <c r="B20" s="5" t="inlineStr">
         <is>
+          <t>540 10</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>DENTAL CLINIC</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="E20" s="6">
+        <f>'54010'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>722 10</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>GALLEY/MESS HALL</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="E21" s="6">
+        <f>'72210'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
           <t>852 10</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>PARKING AREA</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>GSY</t>
         </is>
       </c>
-      <c r="E20" s="6">
+      <c r="E22" s="6">
         <f>'85210'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>851 22</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>VEHICLE STAGING AREA</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>GSY</t>
         </is>
       </c>
-      <c r="E21" s="6">
+      <c r="E23" s="6">
         <f>'85122'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="5" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>851 21</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>VEH. PARK, UNSURFACED</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>GSY</t>
         </is>
       </c>
-      <c r="E22" s="6">
+      <c r="E24" s="6">
         <f>'85121'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>872 10</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>SECURTY/PERIMTR FENCE/WALL</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>LF</t>
         </is>
       </c>
-      <c r="E23" s="6">
+      <c r="E25" s="6">
         <f>'87210'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>872 50</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>ENTRY GATE</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>LF</t>
         </is>
       </c>
-      <c r="E24" s="6">
+      <c r="E26" s="6">
         <f>'87250'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="5" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>872 30</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>MECH SEC BARRICADE</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="E25" s="6">
+      <c r="E27" s="6">
         <f>'87230'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>831 43</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>HAZ WASTE BLDG</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>GSF</t>
         </is>
       </c>
-      <c r="E26" s="6">
+      <c r="E28" s="6">
         <f>'83143'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>831 41</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>HAZARD WSTE STOR &amp; TRANSFR</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>GSF</t>
         </is>
       </c>
-      <c r="E27" s="6">
+      <c r="E29" s="6">
         <f>'83141'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="5" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>811 60</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>STANDBY GENERATOR PLANT</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>KW</t>
         </is>
       </c>
-      <c r="E28" s="6">
+      <c r="E30" s="6">
         <f>'81160'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>880 10</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>FIRE ALARM COMM LINES</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="E29" s="6">
+      <c r="E31" s="6">
         <f>'88010'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>852 35</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>OTHER PAVED AREA</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>GSY</t>
         </is>
       </c>
-      <c r="E30" s="6">
+      <c r="E32" s="6">
         <f>'85235'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="5" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>852 40</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>MISC OPEN STRG/LAYDOWN</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>GSY</t>
         </is>
       </c>
-      <c r="E31" s="6">
+      <c r="E33" s="6">
         <f>'85240'!H37</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="7" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="9">
-        <f>SUM(E9:E31)</f>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="9">
+        <f>SUM(E9:E33)</f>
         <v/>
       </c>
     </row>
@@ -3663,6 +3709,1144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AF58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>540 10</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>DENTAL CLINIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 540 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE SPACE CALCULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Dental Clinic Space</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>SF / Person</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Navy Dental Officers</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="14">
+        <f>V9*Y9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Dental Techs (L33A)</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB10" s="14">
+        <f>V10*Y10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Total NSF</t>
+        </is>
+      </c>
+      <c r="AB11" s="14">
+        <f>SUM(AB9:AB10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1"/>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SPACE REQUIREMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>NTG Factor = 1.33, Required GSF = ROUNDUP(NSF * NTG, 0)</t>
+        </is>
+      </c>
+      <c r="V14" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y14" s="25" t="inlineStr"/>
+      <c r="AB14" s="14">
+        <f>ROUNDUP(AB11*V14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB14</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 500 Series; version date 2023-03-17</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_500series_03_17_2023.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [11, 12, 13]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Table 54010-1 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2 | 93 sq.m. / 1000 GSF</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    3 | 93 sq.m. / 1000 GSF</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    4 | 84 sq.m. / 900 GSF</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    6 | 84 sq.m. / 900 GSF</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    8 | 75 sq.m. / 800 GSF</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    10 | 75 sq.m. / 800 GSF</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="22" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    12 | 70 sq.m. / 750 GSF</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="22" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    18 | 70 sq.m. / 750 GSF</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="22" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ... and 5 more rows; see audit/PLANNING_FACTORS.yaml CCN 54010</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="22" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Table 54010-2 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="22" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1 | 25 sq. m./ 270 GSF</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="21" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="22" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2 | 46 sq. m. / 500 GSF</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="22" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_13_table_3 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="21" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="22" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    3 | 60 sq. m. / 650 GSF</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="21" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="59">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="Y14:AA14"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="AB14:AF14"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="A14:U14"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="A7:AF7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="A11:AA11"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>722 10</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>GALLEY/MESS HALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 722 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE SPACE CALCULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Galley/Mess Hall Space (CLB-4 cooks; FC 2-000-05N Series 700 CCN 722 10 PN-driven authoritative formula in BFR Generator pages 29-35)</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>SF / Person</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Food Service Officer / Chief</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="14">
+        <f>V9*Y9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Food Service Specialists (3381)</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB10" s="14">
+        <f>V10*Y10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Total NSF</t>
+        </is>
+      </c>
+      <c r="AB11" s="14">
+        <f>SUM(AB9:AB10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1"/>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SPACE REQUIREMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>NTG Factor = 1.33, Required GSF = ROUNDUP(NSF * NTG, 0)</t>
+        </is>
+      </c>
+      <c r="V14" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y14" s="25" t="inlineStr"/>
+      <c r="AB14" s="14">
+        <f>ROUNDUP(AB11*V14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB14</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 700 Series; version date 2025-11-19</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_700series_11_19_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [29, 30, 31, 32, 33, 34, 35]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_30_table_1 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Service Schools | 85 %</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Permanent Party</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Construction Battalions | 70 %</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Naval Stations | 70 %</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Personnel Transfer and Overseas Processing Centers | 50 %</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Remote Locations (1) | 90 %</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="22" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_31_table_2 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="22" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Brig | 100 %</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="22" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_32_table_3 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="22" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Infrequent (rural/remote) | 15-20% of net area | 20-25% of net area</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="22" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>UoM source: CCN_VOCABULARY.json (Appendix A 2019-06-27); Series PDF heading omitted UoM, ratifier should verify against current Series text</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="21" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="Y14:AA14"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="AB14:AF14"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="A14:U14"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="A7:AF7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="A11:AA11"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AF72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4463,7 +5647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4891,988 +6075,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AF45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.8164" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="8" customWidth="1" min="23" max="23"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="25"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="8" customWidth="1" min="31" max="31"/>
-    <col width="8" customWidth="1" min="32" max="32"/>
-    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
-    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1"/>
-    <row r="3" ht="30.75" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Installation:</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MCB CAMP BUTLER</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Tenant:</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>CLB 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="14.5" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Installation UIC:</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>M67400</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Tenant UIC:</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>M29030</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>Planning Area: SW</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CCN:</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>851 21</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Nomenclature:</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>VEH. PARK, UNSURFACED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28.5" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 851 21  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="14.5" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>VEH. PARK, UNSURFACED (Loading driver: Vehicular Parking Unsurfaced (SY); FAC 8522; calculated using 85210 criteria when used; CLB-4 sets to 0 because primary parking is paved per 85210)</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>GSY</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Primary loading row</t>
-        </is>
-      </c>
-      <c r="V8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="14">
-        <f>V8*Y8*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="V9" s="13" t="inlineStr"/>
-      <c r="Y9" s="13" t="inlineStr"/>
-      <c r="AB9" s="14">
-        <f>V9*Y9*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="Y10" s="13" t="inlineStr"/>
-      <c r="AB10" s="14">
-        <f>V10*Y10*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
-      <c r="AB11" s="14">
-        <f>V11*Y11*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="Y12" s="13" t="inlineStr"/>
-      <c r="AB12" s="14">
-        <f>V12*Y12*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="V13" s="13" t="inlineStr"/>
-      <c r="Y13" s="13" t="inlineStr"/>
-      <c r="AB13" s="14">
-        <f>V13*Y13*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Subtotal NSF</t>
-        </is>
-      </c>
-      <c r="AB15" s="14">
-        <f>SUM(AB8:AF13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Net to Gross multiplier (NTG = 1.0)</t>
-        </is>
-      </c>
-      <c r="AB16" s="14">
-        <f>AB15*1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>TOTAL REQUIREMENT:</t>
-        </is>
-      </c>
-      <c r="H37" s="26">
-        <f>AB16</f>
-        <v/>
-      </c>
-      <c r="O37" s="18" t="inlineStr">
-        <is>
-          <t>GSY</t>
-        </is>
-      </c>
-      <c r="AB37" s="19" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="21" t="n"/>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="21" t="n"/>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="22" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
-        </is>
-      </c>
-      <c r="C41" s="21" t="n"/>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="21" t="n"/>
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="22" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="n"/>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="21" t="n"/>
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="22" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>Pages: [59]</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="n"/>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="21" t="n"/>
-      <c r="F43" s="21" t="n"/>
-      <c r="G43" s="21" t="n"/>
-      <c r="H43" s="22" t="n"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
-        </is>
-      </c>
-      <c r="C44" s="21" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="21" t="n"/>
-      <c r="G44" s="21" t="n"/>
-      <c r="H44" s="22" t="n"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  e.g. 85121-1: DEFINITION. An unpaved surface for parking and/or staging private</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="22" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="Y4:AF4"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="A7:U7"/>
-    <mergeCell ref="AB15:AF15"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="A16:AA16"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="A12:U12"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="R3:AC3"/>
-    <mergeCell ref="Y13:AA13"/>
-    <mergeCell ref="A6:AF6"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="AB16:AF16"/>
-    <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="AB9:AF9"/>
-    <mergeCell ref="V7:X7"/>
-    <mergeCell ref="A8:U8"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="AB12:AF12"/>
-    <mergeCell ref="R4:X4"/>
-    <mergeCell ref="AB11:AF11"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="F3:L3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="Y8:AA8"/>
-    <mergeCell ref="A10:U10"/>
-    <mergeCell ref="V12:X12"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="R5:AF5"/>
-    <mergeCell ref="A13:U13"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="M3:Q3"/>
-    <mergeCell ref="A9:U9"/>
-    <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="AB13:AF13"/>
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="A15:AA15"/>
-    <mergeCell ref="A1:AF2"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="A11:U11"/>
-    <mergeCell ref="AB10:AF10"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="AB37:AF37"/>
-    <mergeCell ref="M4:Q4"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="84"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AF54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.8164" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="8" customWidth="1" min="23" max="23"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="25"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="8" customWidth="1" min="31" max="31"/>
-    <col width="8" customWidth="1" min="32" max="32"/>
-    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
-    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1"/>
-    <row r="3" ht="30.75" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Installation:</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MCB CAMP BUTLER</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Tenant:</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>CLB 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="14.5" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Installation UIC:</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>M67400</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Tenant UIC:</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>M29030</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>Planning Area: SW</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CCN:</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>872 10</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Nomenclature:</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>SECURTY/PERIMTR FENCE/WALL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28.5" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="14.5" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>SECURTY/PERIMTR FENCE/WALL (Loading driver: Station Security and Perimeter Fencing (LF); FAC 8721; standard 7-ft chain link with 1.5-ft outriggers and 3 strands BB; min 50-150 ft from buildings/critical supplies; SRC I/II ammo fence per DoDM 5100.76 + UFC 4-022-03; CLB-4 placeholder 2000 LF pending compound perimeter survey)</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>LF</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Primary loading row</t>
-        </is>
-      </c>
-      <c r="V8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="13" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AB8" s="14">
-        <f>V8*Y8*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="V9" s="13" t="inlineStr"/>
-      <c r="Y9" s="13" t="inlineStr"/>
-      <c r="AB9" s="14">
-        <f>V9*Y9*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="Y10" s="13" t="inlineStr"/>
-      <c r="AB10" s="14">
-        <f>V10*Y10*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
-      <c r="AB11" s="14">
-        <f>V11*Y11*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="Y12" s="13" t="inlineStr"/>
-      <c r="AB12" s="14">
-        <f>V12*Y12*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="V13" s="13" t="inlineStr"/>
-      <c r="Y13" s="13" t="inlineStr"/>
-      <c r="AB13" s="14">
-        <f>V13*Y13*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Subtotal NSF</t>
-        </is>
-      </c>
-      <c r="AB15" s="14">
-        <f>SUM(AB8:AF13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Net to Gross multiplier (NTG = 1.0)</t>
-        </is>
-      </c>
-      <c r="AB16" s="14">
-        <f>AB15*1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>TOTAL REQUIREMENT:</t>
-        </is>
-      </c>
-      <c r="H37" s="27">
-        <f>AB16</f>
-        <v/>
-      </c>
-      <c r="O37" s="18" t="inlineStr">
-        <is>
-          <t>LF</t>
-        </is>
-      </c>
-      <c r="AB37" s="19" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="21" t="n"/>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="21" t="n"/>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="22" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
-        </is>
-      </c>
-      <c r="C41" s="21" t="n"/>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="21" t="n"/>
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="22" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="n"/>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="21" t="n"/>
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="22" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>Pages: [70, 71, 72]</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="n"/>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="21" t="n"/>
-      <c r="F43" s="21" t="n"/>
-      <c r="G43" s="21" t="n"/>
-      <c r="H43" s="22" t="n"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Table 87210-1 (); loading driver: TBD</t>
-        </is>
-      </c>
-      <c r="C44" s="21" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="21" t="n"/>
-      <c r="G44" s="21" t="n"/>
-      <c r="H44" s="22" t="n"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Magazines storing SRC I &amp; II A&amp;E | Restricted Areas — as defined in DoDM 5100.76 | Fence fabric shall be chain link, i.e., galvanized, aluminized, or plastic- coated woven steel, 2-inch square mesh made from 9- gauge diameter wire, excluding coating that meets Federal Specification RR-F-191K. | Refer to DoDM 5100.76</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="22" t="n"/>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="B46" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Non-metallic Security Fence Requirement | Where restrictions of visibility into activity is desired. | Wooden Security fence | Refer to OPNAVINST 5530.14E</t>
-        </is>
-      </c>
-      <c r="C46" s="21" t="n"/>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="21" t="n"/>
-      <c r="F46" s="21" t="n"/>
-      <c r="G46" s="21" t="n"/>
-      <c r="H46" s="22" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    At radio direction-finder structures. | Wooden Security fence</t>
-        </is>
-      </c>
-      <c r="C47" s="21" t="n"/>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="21" t="n"/>
-      <c r="F47" s="21" t="n"/>
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="22" t="n"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Where chain link materials are not available. | Wooden Security fence</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="22" t="n"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Protection of sports facilities, users and spectators | Athletic courts. | Chain link. | 10-12 | --</t>
-        </is>
-      </c>
-      <c r="C49" s="21" t="n"/>
-      <c r="D49" s="21" t="n"/>
-      <c r="E49" s="21" t="n"/>
-      <c r="F49" s="21" t="n"/>
-      <c r="G49" s="21" t="n"/>
-      <c r="H49" s="22" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="B50" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Swimming pools. | Chain link or decorative wood. | 6 | --</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="21" t="n"/>
-      <c r="E50" s="21" t="n"/>
-      <c r="F50" s="21" t="n"/>
-      <c r="G50" s="21" t="n"/>
-      <c r="H50" s="22" t="n"/>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="B51" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Playgrounds. | Chain link or decorative wood. | 5 | --</t>
-        </is>
-      </c>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="21" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
-      <c r="H51" s="22" t="n"/>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="B52" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Snow fencing | Where drifting snow is a problem. | Picket interwoven with wire- studded metal posts | 4 | --</t>
-        </is>
-      </c>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="22" t="n"/>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="B53" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ... and 12 more rows; see audit/PLANNING_FACTORS.yaml CCN 87210</t>
-        </is>
-      </c>
-      <c r="C53" s="21" t="n"/>
-      <c r="D53" s="21" t="n"/>
-      <c r="E53" s="21" t="n"/>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="21" t="n"/>
-      <c r="H53" s="22" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  page_72_table_2 (); loading driver: TBD</t>
-        </is>
-      </c>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="21" t="n"/>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="22" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="Y4:AF4"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="A7:U7"/>
-    <mergeCell ref="AB15:AF15"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="A16:AA16"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="B51:H51"/>
-    <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="A12:U12"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="B50:H50"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="R3:AC3"/>
-    <mergeCell ref="Y13:AA13"/>
-    <mergeCell ref="A6:AF6"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="AB16:AF16"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="AB9:AF9"/>
-    <mergeCell ref="V7:X7"/>
-    <mergeCell ref="A8:U8"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="AB12:AF12"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="R4:X4"/>
-    <mergeCell ref="AB11:AF11"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="F3:L3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="Y8:AA8"/>
-    <mergeCell ref="A10:U10"/>
-    <mergeCell ref="V12:X12"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="R5:AF5"/>
-    <mergeCell ref="A13:U13"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B48:H48"/>
-    <mergeCell ref="M3:Q3"/>
-    <mergeCell ref="A9:U9"/>
-    <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="AB13:AF13"/>
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="A15:AA15"/>
-    <mergeCell ref="A1:AF2"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="A11:U11"/>
-    <mergeCell ref="AB10:AF10"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="AB37:AF37"/>
-    <mergeCell ref="M4:Q4"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="84"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5983,7 +6185,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>872 50</t>
+          <t>851 21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5993,21 +6195,21 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>ENTRY GATE</t>
+          <t>VEH. PARK, UNSURFACED</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28.5" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 50  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 851 21  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>ENTRY GATE (Loading driver: Entry Gate (LF); FAC 8721; CCN added Jan 2024; CLB-4 default 30 LF for 1-2 main gates pending site survey)</t>
+          <t>VEH. PARK, UNSURFACED (Loading driver: Vehicular Parking Unsurfaced (SY); FAC 8522; calculated using 85210 criteria when used; CLB-4 sets to 0 because primary parking is paved per 85210)</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -6022,7 +6224,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>GSY</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6238,7 @@
         <v>1</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="14">
         <f>V8*Y8*1.0</f>
@@ -6137,13 +6339,13 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="27">
+      <c r="H37" s="26">
         <f>AB16</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>GSY</t>
         </is>
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
@@ -6190,7 +6392,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Pages: [73]</t>
+          <t>Pages: [59]</t>
         </is>
       </c>
       <c r="C43" s="21" t="n"/>
@@ -6216,7 +6418,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  e.g. 87250-1: ENTRY GATE. An entry gate is the frame, gate, or other apparatus that</t>
+          <t xml:space="preserve">  e.g. 85121-1: DEFINITION. An unpaved surface for parking and/or staging private</t>
         </is>
       </c>
       <c r="C45" s="21" t="n"/>
@@ -7330,8 +7532,16 @@
       <c r="B28" t="n">
         <v>22</v>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -7412,8 +7622,16 @@
       <c r="B30" t="n">
         <v>24</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -7494,8 +7712,16 @@
       <c r="B32" t="n">
         <v>26</v>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -7531,8 +7757,16 @@
       <c r="B33" t="n">
         <v>27</v>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -9728,8 +9962,16 @@
       <c r="B82" t="n">
         <v>76</v>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -9765,8 +10007,16 @@
       <c r="B83" t="n">
         <v>77</v>
       </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -9802,8 +10052,16 @@
       <c r="B84" t="n">
         <v>78</v>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -9839,8 +10097,16 @@
       <c r="B85" t="n">
         <v>79</v>
       </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -9876,8 +10142,16 @@
       <c r="B86" t="n">
         <v>80</v>
       </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -9913,8 +10187,16 @@
       <c r="B87" t="n">
         <v>81</v>
       </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -9950,8 +10232,16 @@
       <c r="B88" t="n">
         <v>82</v>
       </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -9987,8 +10277,16 @@
       <c r="B89" t="n">
         <v>83</v>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -10024,8 +10322,16 @@
       <c r="B90" t="n">
         <v>84</v>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -10061,8 +10367,16 @@
       <c r="B91" t="n">
         <v>85</v>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>M29111</t>
@@ -10368,8 +10682,16 @@
       <c r="B98" t="n">
         <v>92</v>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>M29112</t>
@@ -10405,8 +10727,16 @@
       <c r="B99" t="n">
         <v>93</v>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>M29112</t>
@@ -12962,8 +13292,16 @@
       <c r="B156" t="n">
         <v>150</v>
       </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>M29113</t>
@@ -12999,8 +13337,16 @@
       <c r="B157" t="n">
         <v>151</v>
       </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
           <t>M29113</t>
@@ -18976,8 +19322,16 @@
       <c r="B290" t="n">
         <v>284</v>
       </c>
-      <c r="C290" t="inlineStr"/>
-      <c r="D290" t="inlineStr"/>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
       <c r="F290" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19013,8 +19367,16 @@
       <c r="B291" t="n">
         <v>285</v>
       </c>
-      <c r="C291" t="inlineStr"/>
-      <c r="D291" t="inlineStr"/>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
       <c r="F291" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19050,8 +19412,16 @@
       <c r="B292" t="n">
         <v>286</v>
       </c>
-      <c r="C292" t="inlineStr"/>
-      <c r="D292" t="inlineStr"/>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
       <c r="F292" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19087,8 +19457,16 @@
       <c r="B293" t="n">
         <v>287</v>
       </c>
-      <c r="C293" t="inlineStr"/>
-      <c r="D293" t="inlineStr"/>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>72210</t>
+        </is>
+      </c>
       <c r="F293" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19124,8 +19502,16 @@
       <c r="B294" t="n">
         <v>288</v>
       </c>
-      <c r="C294" t="inlineStr"/>
-      <c r="D294" t="inlineStr"/>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>54010</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>54010</t>
+        </is>
+      </c>
       <c r="F294" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19161,8 +19547,16 @@
       <c r="B295" t="n">
         <v>289</v>
       </c>
-      <c r="C295" t="inlineStr"/>
-      <c r="D295" t="inlineStr"/>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>54010</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>54010</t>
+        </is>
+      </c>
       <c r="F295" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19198,8 +19592,16 @@
       <c r="B296" t="n">
         <v>290</v>
       </c>
-      <c r="C296" t="inlineStr"/>
-      <c r="D296" t="inlineStr"/>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>54010</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>54010</t>
+        </is>
+      </c>
       <c r="F296" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19235,8 +19637,16 @@
       <c r="B297" t="n">
         <v>291</v>
       </c>
-      <c r="C297" t="inlineStr"/>
-      <c r="D297" t="inlineStr"/>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F297" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19272,8 +19682,16 @@
       <c r="B298" t="n">
         <v>292</v>
       </c>
-      <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr"/>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F298" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19309,8 +19727,16 @@
       <c r="B299" t="n">
         <v>293</v>
       </c>
-      <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr"/>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19346,8 +19772,16 @@
       <c r="B300" t="n">
         <v>294</v>
       </c>
-      <c r="C300" t="inlineStr"/>
-      <c r="D300" t="inlineStr"/>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19518,8 +19952,16 @@
       <c r="B304" t="n">
         <v>298</v>
       </c>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr"/>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F304" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19555,8 +19997,16 @@
       <c r="B305" t="n">
         <v>299</v>
       </c>
-      <c r="C305" t="inlineStr"/>
-      <c r="D305" t="inlineStr"/>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19592,8 +20042,16 @@
       <c r="B306" t="n">
         <v>300</v>
       </c>
-      <c r="C306" t="inlineStr"/>
-      <c r="D306" t="inlineStr"/>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F306" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19629,8 +20087,16 @@
       <c r="B307" t="n">
         <v>301</v>
       </c>
-      <c r="C307" t="inlineStr"/>
-      <c r="D307" t="inlineStr"/>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F307" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19666,8 +20132,16 @@
       <c r="B308" t="n">
         <v>302</v>
       </c>
-      <c r="C308" t="inlineStr"/>
-      <c r="D308" t="inlineStr"/>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F308" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19703,8 +20177,16 @@
       <c r="B309" t="n">
         <v>303</v>
       </c>
-      <c r="C309" t="inlineStr"/>
-      <c r="D309" t="inlineStr"/>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F309" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19740,8 +20222,16 @@
       <c r="B310" t="n">
         <v>304</v>
       </c>
-      <c r="C310" t="inlineStr"/>
-      <c r="D310" t="inlineStr"/>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19777,8 +20267,16 @@
       <c r="B311" t="n">
         <v>305</v>
       </c>
-      <c r="C311" t="inlineStr"/>
-      <c r="D311" t="inlineStr"/>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F311" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19814,8 +20312,16 @@
       <c r="B312" t="n">
         <v>306</v>
       </c>
-      <c r="C312" t="inlineStr"/>
-      <c r="D312" t="inlineStr"/>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F312" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19851,8 +20357,16 @@
       <c r="B313" t="n">
         <v>307</v>
       </c>
-      <c r="C313" t="inlineStr"/>
-      <c r="D313" t="inlineStr"/>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19888,8 +20402,16 @@
       <c r="B314" t="n">
         <v>308</v>
       </c>
-      <c r="C314" t="inlineStr"/>
-      <c r="D314" t="inlineStr"/>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19925,8 +20447,16 @@
       <c r="B315" t="n">
         <v>309</v>
       </c>
-      <c r="C315" t="inlineStr"/>
-      <c r="D315" t="inlineStr"/>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -19962,8 +20492,16 @@
       <c r="B316" t="n">
         <v>310</v>
       </c>
-      <c r="C316" t="inlineStr"/>
-      <c r="D316" t="inlineStr"/>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr">
         <is>
           <t>M29114</t>
@@ -20016,7 +20554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF45"/>
+  <dimension ref="A1:AF54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -20120,7 +20658,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>872 30</t>
+          <t>872 10</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -20130,21 +20668,21 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>MECH SEC BARRICADE</t>
+          <t>SECURTY/PERIMTR FENCE/WALL</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28.5" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 30  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>MECH SEC BARRICADE (Loading driver: Mechanical Security Barricade (EA); FAC 1458; drop arm barriers at gates; CLB-4 default 2 EA (one per gate))</t>
+          <t>SECURTY/PERIMTR FENCE/WALL (Loading driver: Station Security and Perimeter Fencing (LF); FAC 8721; standard 7-ft chain link with 1.5-ft outriggers and 3 strands BB; min 50-150 ft from buildings/critical supplies; SRC I/II ammo fence per DoDM 5100.76 + UFC 4-022-03; CLB-4 placeholder 2000 LF pending compound perimeter survey)</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -20159,7 +20697,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>LF</t>
         </is>
       </c>
     </row>
@@ -20173,7 +20711,7 @@
         <v>1</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AB8" s="14">
         <f>V8*Y8*1.0</f>
@@ -20274,13 +20812,13 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="28">
+      <c r="H37" s="27">
         <f>AB16</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
@@ -20327,7 +20865,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Pages: [73]</t>
+          <t>Pages: [70, 71, 72]</t>
         </is>
       </c>
       <c r="C43" s="21" t="n"/>
@@ -20340,7 +20878,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Engineering-study CCN per NAVFAC doctrine; 2 narrative section(s) captured</t>
+          <t xml:space="preserve">  Table 87210-1 (); loading driver: TBD</t>
         </is>
       </c>
       <c r="C44" s="21" t="n"/>
@@ -20353,7 +20891,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  e.g. 87230-1: DEFINITION. Mechanically operated barricade consisting of pop-up</t>
+          <t xml:space="preserve">    Magazines storing SRC I &amp; II A&amp;E | Restricted Areas — as defined in DoDM 5100.76 | Fence fabric shall be chain link, i.e., galvanized, aluminized, or plastic- coated woven steel, 2-inch square mesh made from 9- gauge diameter wire, excluding coating that meets Federal Specification RR-F-191K. | Refer to DoDM 5100.76</t>
         </is>
       </c>
       <c r="C45" s="21" t="n"/>
@@ -20363,8 +20901,125 @@
       <c r="G45" s="21" t="n"/>
       <c r="H45" s="22" t="n"/>
     </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Non-metallic Security Fence Requirement | Where restrictions of visibility into activity is desired. | Wooden Security fence | Refer to OPNAVINST 5530.14E</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    At radio direction-finder structures. | Wooden Security fence</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Where chain link materials are not available. | Wooden Security fence</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Protection of sports facilities, users and spectators | Athletic courts. | Chain link. | 10-12 | --</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Swimming pools. | Chain link or decorative wood. | 6 | --</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="22" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Playgrounds. | Chain link or decorative wood. | 5 | --</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="22" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Snow fencing | Where drifting snow is a problem. | Picket interwoven with wire- studded metal posts | 4 | --</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="22" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ... and 12 more rows; see audit/PLANNING_FACTORS.yaml CCN 87210</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="22" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_72_table_2 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="67">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
@@ -20373,27 +21028,34 @@
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
     <mergeCell ref="V9:X9"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="A16:AA16"/>
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B51:H51"/>
     <mergeCell ref="Y7:AA7"/>
     <mergeCell ref="B45:H45"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B50:H50"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B54:H54"/>
     <mergeCell ref="Y12:AA12"/>
     <mergeCell ref="AB9:AF9"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="B52:H52"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
     <mergeCell ref="B43:H43"/>
@@ -20406,6 +21068,7 @@
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
     <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B48:H48"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -20416,6 +21079,7 @@
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>
@@ -20548,7 +21212,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>831 43</t>
+          <t>872 50</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -20558,21 +21222,21 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>HAZ WASTE BLDG</t>
+          <t>ENTRY GATE</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28.5" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 831 43  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 50  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>HAZ WASTE BLDG (Loading driver: Hazardous Waste Storage Building (SF); FAC 4423; 150-meter buffer from inhabited areas, ammo, or POL stores; short-term &lt;90 days vs long-term &gt;90 days; CLB-4 placeholder 400 SF for unit HAZMAT point)</t>
+          <t>ENTRY GATE (Loading driver: Entry Gate (LF); FAC 8721; CCN added Jan 2024; CLB-4 default 30 LF for 1-2 main gates pending site survey)</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -20587,7 +21251,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>GSF</t>
+          <t>LF</t>
         </is>
       </c>
     </row>
@@ -20601,7 +21265,7 @@
         <v>1</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="AB8" s="14">
         <f>V8*Y8*1.0</f>
@@ -20702,13 +21366,13 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="27">
         <f>AB16</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
         <is>
-          <t>GSF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
@@ -20755,7 +21419,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Pages: [42]</t>
+          <t>Pages: [73]</t>
         </is>
       </c>
       <c r="C43" s="21" t="n"/>
@@ -20781,7 +21445,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  e.g. 83143-1: DEFINITION. Use this category code for facilities that are buildings used</t>
+          <t xml:space="preserve">  e.g. 87250-1: ENTRY GATE. An entry gate is the frame, gate, or other apparatus that</t>
         </is>
       </c>
       <c r="C45" s="21" t="n"/>
@@ -20976,7 +21640,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>831 41</t>
+          <t>872 30</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -20986,21 +21650,21 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>HAZARD WSTE STOR &amp; TRANSFR</t>
+          <t>MECH SEC BARRICADE</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28.5" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 831 41  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 30  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>HAZARD WSTE STOR &amp; TRANSFR (Loading driver: Hazardous Waste Storage and Transfer Facility (EA); FAC 8926; non-building structures; same 150-meter buffer rule; CLB-4 default 1 EA)</t>
+          <t>MECH SEC BARRICADE (Loading driver: Mechanical Security Barricade (EA); FAC 1458; drop arm barriers at gates; CLB-4 default 2 EA (one per gate))</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -21015,7 +21679,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>GSF</t>
+          <t>EA</t>
         </is>
       </c>
     </row>
@@ -21029,7 +21693,7 @@
         <v>1</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="14">
         <f>V8*Y8*1.0</f>
@@ -21130,13 +21794,13 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="28">
         <f>AB16</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
         <is>
-          <t>GSF</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
@@ -21183,7 +21847,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Pages: [40]</t>
+          <t>Pages: [73]</t>
         </is>
       </c>
       <c r="C43" s="21" t="n"/>
@@ -21196,7 +21860,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Engineering-study CCN per NAVFAC doctrine; 3 narrative section(s) captured</t>
+          <t>Engineering-study CCN per NAVFAC doctrine; 2 narrative section(s) captured</t>
         </is>
       </c>
       <c r="C44" s="21" t="n"/>
@@ -21209,7 +21873,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  e.g. 83141-1: DEFINITION. Use this category code for facilities that are structures (non-</t>
+          <t xml:space="preserve">  e.g. 87230-1: DEFINITION. Mechanically operated barricade consisting of pop-up</t>
         </is>
       </c>
       <c r="C45" s="21" t="n"/>
@@ -21300,6 +21964,862 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>831 43</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>HAZ WASTE BLDG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 831 43  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>HAZ WASTE BLDG (Loading driver: Hazardous Waste Storage Building (SF); FAC 4423; 150-meter buffer from inhabited areas, ammo, or POL stores; short-term &lt;90 days vs long-term &gt;90 days; CLB-4 placeholder 400 SF for unit HAZMAT point)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [42]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 83143-1: DEFINITION. Use this category code for facilities that are buildings used</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>831 41</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>HAZARD WSTE STOR &amp; TRANSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 831 41  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>HAZARD WSTE STOR &amp; TRANSFR (Loading driver: Hazardous Waste Storage and Transfer Facility (EA); FAC 8926; non-building structures; same 150-meter buffer rule; CLB-4 default 1 EA)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 800 Series; version date 2025-03-31</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_800series_03_31_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [40]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 3 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 83141-1: DEFINITION. Use this category code for facilities that are structures (non-</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AF46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -21736,7 +23256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22178,7 +23698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22606,7 +24126,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
